--- a/artfynd/A 58209-2025 artfynd.xlsx
+++ b/artfynd/A 58209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221002</v>
+        <v>125221006</v>
       </c>
       <c r="B2" t="n">
-        <v>92535</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659027</v>
+        <v>658822</v>
       </c>
       <c r="R2" t="n">
-        <v>7201497</v>
+        <v>7201833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221005</v>
+        <v>125221003</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658937</v>
+        <v>658927</v>
       </c>
       <c r="R3" t="n">
-        <v>7201750</v>
+        <v>7201735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221004</v>
+        <v>125221002</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658936</v>
+        <v>659027</v>
       </c>
       <c r="R4" t="n">
-        <v>7201748</v>
+        <v>7201497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221006</v>
+        <v>121150389</v>
       </c>
       <c r="B5" t="n">
-        <v>92527</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1038,22 +1038,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrbyberg, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658822</v>
+        <v>658753</v>
       </c>
       <c r="R5" t="n">
-        <v>7201833</v>
+        <v>7201892</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1096,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221003</v>
+        <v>125221005</v>
       </c>
       <c r="B6" t="n">
-        <v>92529</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1157,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658927</v>
+        <v>658937</v>
       </c>
       <c r="R6" t="n">
-        <v>7201735</v>
+        <v>7201750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,6 +1218,222 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121150388</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrbyberg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658753</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7201892</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125221004</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrbyberg, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>658936</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7201748</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58209-2025 artfynd.xlsx
+++ b/artfynd/A 58209-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221006</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150389</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150388</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,8 +1469,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125221004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>